--- a/data/monthly_place/【2025年7月】月次配置.xlsx
+++ b/data/monthly_place/【2025年7月】月次配置.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="528" windowWidth="21792" windowHeight="8868"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="70">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -143,9 +142,6 @@
     <t>Instagramストーリーズ</t>
   </si>
   <si>
-    <t>Instagram投稿: おいしいクレープ屋さんがあなたの街に！！</t>
-  </si>
-  <si>
     <t>archived</t>
   </si>
   <si>
@@ -165,31 +161,93 @@
   </si>
   <si>
     <t>竹内歯科クリニック（審美ジルコニア）</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>発見ホーム</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>通算</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【銀座トレーニングラボ】
+“脚が変わる”は、立ち方から始まる。...</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -197,36 +255,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,14 +573,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:AB17"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB68"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +663,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -637,7 +692,7 @@
         <v>48</v>
       </c>
       <c r="L2">
-        <v>1.020833</v>
+        <v>1.0208330000000001</v>
       </c>
       <c r="N2">
         <v>160</v>
@@ -655,7 +710,7 @@
         <v>49</v>
       </c>
       <c r="S2">
-        <v>591.836735</v>
+        <v>591.83673499999998</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -667,7 +722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -714,7 +769,7 @@
         <v>12</v>
       </c>
       <c r="S3">
-        <v>333.333333</v>
+        <v>333.33333299999998</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -726,7 +781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -782,7 +837,7 @@
         <v>26</v>
       </c>
       <c r="S4">
-        <v>653.846154</v>
+        <v>653.84615399999996</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -791,19 +846,19 @@
         <v>17</v>
       </c>
       <c r="W4">
-        <v>3.846154</v>
+        <v>3.8461539999999999</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>3.846154</v>
+        <v>3.8461539999999999</v>
       </c>
       <c r="Z4">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -838,7 +893,7 @@
         <v>145</v>
       </c>
       <c r="L5">
-        <v>1.041379</v>
+        <v>1.0413790000000001</v>
       </c>
       <c r="M5">
         <v>121</v>
@@ -859,7 +914,7 @@
         <v>151</v>
       </c>
       <c r="S5">
-        <v>801.324503</v>
+        <v>801.32450300000005</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -868,19 +923,19 @@
         <v>121</v>
       </c>
       <c r="W5">
-        <v>0.662252</v>
+        <v>0.66225199999999995</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>0.662252</v>
+        <v>0.66225199999999995</v>
       </c>
       <c r="Z5">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -888,7 +943,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -900,72 +955,54 @@
         <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
         <v>35</v>
       </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
       <c r="K6">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="L6">
-        <v>1.021978</v>
-      </c>
-      <c r="M6">
-        <v>27.66666667</v>
-      </c>
-      <c r="N6">
-        <v>160</v>
-      </c>
-      <c r="O6" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6">
+        <v>12</v>
+      </c>
+      <c r="S6">
+        <v>583.33333300000004</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
         <v>44</v>
-      </c>
-      <c r="R6">
-        <v>93</v>
-      </c>
-      <c r="S6">
-        <v>892.473118</v>
-      </c>
-      <c r="T6">
-        <v>3</v>
-      </c>
-      <c r="V6">
-        <v>27.666667</v>
-      </c>
-      <c r="W6">
-        <v>3.225806</v>
-      </c>
-      <c r="X6">
-        <v>4</v>
-      </c>
-      <c r="Y6">
-        <v>4.301075</v>
-      </c>
-      <c r="Z6">
-        <v>20.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -977,54 +1014,54 @@
         <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
         <v>35</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
-      <c r="N7">
-        <v>160</v>
-      </c>
-      <c r="O7" t="s">
-        <v>36</v>
+      <c r="N7" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
       </c>
       <c r="P7">
         <v>3</v>
       </c>
       <c r="Q7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>1000</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
         <v>44</v>
-      </c>
-      <c r="R7">
-        <v>6</v>
-      </c>
-      <c r="S7">
-        <v>500</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
@@ -1036,72 +1073,54 @@
         <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
       </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>40</v>
-      </c>
       <c r="K8">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
-      <c r="M8">
-        <v>19</v>
-      </c>
-      <c r="N8">
-        <v>160</v>
-      </c>
-      <c r="O8" t="s">
-        <v>36</v>
+      <c r="N8" t="s">
+        <v>46</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>1000</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
         <v>44</v>
-      </c>
-      <c r="R8">
-        <v>17</v>
-      </c>
-      <c r="S8">
-        <v>1117.647059</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>19</v>
-      </c>
-      <c r="W8">
-        <v>5.882353</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>5.882353</v>
-      </c>
-      <c r="Z8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>31</v>
@@ -1113,7 +1132,7 @@
         <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
         <v>35</v>
@@ -1125,52 +1144,52 @@
         <v>40</v>
       </c>
       <c r="K9">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
       <c r="M9">
-        <v>23</v>
-      </c>
-      <c r="N9">
-        <v>160</v>
-      </c>
-      <c r="O9" t="s">
-        <v>36</v>
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R9">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S9">
-        <v>696.969697</v>
+        <v>896.55172400000004</v>
       </c>
       <c r="T9">
         <v>1</v>
       </c>
       <c r="V9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="W9">
-        <v>3.030303</v>
+        <v>3.4482759999999999</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>3.030303</v>
+        <v>3.4482759999999999</v>
       </c>
       <c r="Z9">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1178,7 +1197,7 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -1190,54 +1209,54 @@
         <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>35</v>
       </c>
       <c r="K10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
       <c r="N10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="s">
         <v>47</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="R10">
+        <v>6</v>
+      </c>
+      <c r="S10">
+        <v>1000</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>48</v>
-      </c>
-      <c r="R10">
-        <v>12</v>
-      </c>
-      <c r="S10">
-        <v>583.333333</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>31</v>
@@ -1249,19 +1268,19 @@
         <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
         <v>35</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1270,33 +1289,33 @@
         <v>3</v>
       </c>
       <c r="Q11" t="s">
+        <v>47</v>
+      </c>
+      <c r="R11">
+        <v>4</v>
+      </c>
+      <c r="S11">
+        <v>750</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
         <v>48</v>
-      </c>
-      <c r="R11">
-        <v>3</v>
-      </c>
-      <c r="S11">
-        <v>1000</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -1308,7 +1327,7 @@
         <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s">
         <v>35</v>
@@ -1320,22 +1339,22 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
+        <v>46</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="s">
         <v>47</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>48</v>
       </c>
       <c r="R12">
         <v>2</v>
       </c>
       <c r="S12">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="X12">
         <v>0</v>
@@ -1347,7 +1366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1355,7 +1374,7 @@
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>31</v>
@@ -1367,311 +1386,3918 @@
         <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H13" t="s">
         <v>35</v>
       </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="K13">
+        <v>27</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="N13" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>41</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>47</v>
+      </c>
+      <c r="R13">
+        <v>27</v>
+      </c>
+      <c r="S13">
+        <v>1518.518519</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14">
+        <v>18</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>59000</v>
+      </c>
+      <c r="O14" t="s">
+        <v>68</v>
+      </c>
+      <c r="P14">
+        <v>19</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>43</v>
+      </c>
+      <c r="R14">
+        <v>18</v>
+      </c>
+      <c r="S14">
+        <v>1055.555556</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15">
+        <v>9</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>59000</v>
+      </c>
+      <c r="O15" t="s">
+        <v>68</v>
+      </c>
+      <c r="P15">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15">
+        <v>9</v>
+      </c>
+      <c r="S15">
+        <v>444.44444399999998</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>59000</v>
+      </c>
+      <c r="O16" t="s">
+        <v>68</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17">
+        <v>21</v>
+      </c>
+      <c r="L17">
+        <v>1.380952</v>
+      </c>
+      <c r="N17" t="s">
+        <v>46</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>29</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>47</v>
+      </c>
+      <c r="R17">
+        <v>29</v>
+      </c>
+      <c r="S17">
+        <v>1000</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
         <v>40</v>
       </c>
-      <c r="K13">
-        <v>29</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
+      <c r="K18">
+        <v>28</v>
+      </c>
+      <c r="L18">
+        <v>1.714286</v>
+      </c>
+      <c r="M18">
+        <v>82</v>
+      </c>
+      <c r="N18" t="s">
+        <v>46</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>82</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>47</v>
+      </c>
+      <c r="R18">
+        <v>48</v>
+      </c>
+      <c r="S18">
+        <v>1708.333333</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>82</v>
+      </c>
+      <c r="W18">
+        <v>2.0833330000000001</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>2.0833330000000001</v>
+      </c>
+      <c r="Z18">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19">
+        <v>38</v>
+      </c>
+      <c r="J19" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19">
+        <v>1137</v>
+      </c>
+      <c r="L19">
+        <v>2.796834</v>
+      </c>
+      <c r="M19">
+        <v>75.815789469999999</v>
+      </c>
+      <c r="N19" t="s">
+        <v>46</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>2881</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>47</v>
+      </c>
+      <c r="R19">
+        <v>3180</v>
+      </c>
+      <c r="S19">
+        <v>905.97484299999996</v>
+      </c>
+      <c r="T19">
+        <v>38</v>
+      </c>
+      <c r="V19">
+        <v>75.815788999999995</v>
+      </c>
+      <c r="W19">
+        <v>1.1949689999999999</v>
+      </c>
+      <c r="X19">
+        <v>42</v>
+      </c>
+      <c r="Y19">
+        <v>1.3207549999999999</v>
+      </c>
+      <c r="Z19">
+        <v>68.595237999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="J20" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20">
+        <v>135</v>
+      </c>
+      <c r="L20">
+        <v>1.0962959999999999</v>
+      </c>
+      <c r="M20">
+        <v>35.375</v>
+      </c>
+      <c r="N20" t="s">
+        <v>46</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>283</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>65</v>
+      </c>
+      <c r="R20">
+        <v>148</v>
+      </c>
+      <c r="S20">
+        <v>1912.1621620000001</v>
+      </c>
+      <c r="T20">
+        <v>8</v>
+      </c>
+      <c r="V20">
+        <v>35.375</v>
+      </c>
+      <c r="W20">
+        <v>5.405405</v>
+      </c>
+      <c r="X20">
+        <v>9</v>
+      </c>
+      <c r="Y20">
+        <v>6.0810810000000002</v>
+      </c>
+      <c r="Z20">
+        <v>31.444444000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21">
+        <v>67</v>
+      </c>
+      <c r="L21">
+        <v>1.1791039999999999</v>
+      </c>
+      <c r="N21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>47</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>65</v>
+      </c>
+      <c r="R21">
+        <v>79</v>
+      </c>
+      <c r="S21">
+        <v>594.93670899999995</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>46</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>65</v>
+      </c>
+      <c r="R22">
+        <v>3</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23">
+        <v>108</v>
+      </c>
+      <c r="L23">
+        <v>1.1944440000000001</v>
+      </c>
+      <c r="M23">
+        <v>90</v>
+      </c>
+      <c r="N23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>90</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>65</v>
+      </c>
+      <c r="R23">
+        <v>129</v>
+      </c>
+      <c r="S23">
+        <v>697.67441899999994</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>90</v>
+      </c>
+      <c r="W23">
+        <v>0.77519400000000005</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>0.77519400000000005</v>
+      </c>
+      <c r="Z23">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>43</v>
+      </c>
+      <c r="J24" t="s">
+        <v>40</v>
+      </c>
+      <c r="K24">
+        <v>2169</v>
+      </c>
+      <c r="L24">
+        <v>1.2120789999999999</v>
+      </c>
+      <c r="M24">
+        <v>62.627906979999999</v>
+      </c>
+      <c r="N24" t="s">
+        <v>46</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>2693</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>65</v>
+      </c>
+      <c r="R24">
+        <v>2629</v>
+      </c>
+      <c r="S24">
+        <v>1024.3438570000001</v>
+      </c>
+      <c r="T24">
+        <v>43</v>
+      </c>
+      <c r="V24">
+        <v>62.627907</v>
+      </c>
+      <c r="W24">
+        <v>1.6356029999999999</v>
+      </c>
+      <c r="X24">
+        <v>48</v>
+      </c>
+      <c r="Y24">
+        <v>1.8257890000000001</v>
+      </c>
+      <c r="Z24">
+        <v>56.104166999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>54</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25">
+        <v>11</v>
+      </c>
+      <c r="J25" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25">
+        <v>311</v>
+      </c>
+      <c r="L25">
+        <v>1.144695</v>
+      </c>
+      <c r="M25">
+        <v>50.363636360000001</v>
+      </c>
+      <c r="N25" t="s">
+        <v>46</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>554</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>62</v>
+      </c>
+      <c r="R25">
+        <v>356</v>
+      </c>
+      <c r="S25">
+        <v>1556.1797750000001</v>
+      </c>
+      <c r="T25">
+        <v>11</v>
+      </c>
+      <c r="V25">
+        <v>50.363636</v>
+      </c>
+      <c r="W25">
+        <v>3.0898880000000002</v>
+      </c>
+      <c r="X25">
+        <v>11</v>
+      </c>
+      <c r="Y25">
+        <v>3.0898880000000002</v>
+      </c>
+      <c r="Z25">
+        <v>50.363636</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>40</v>
+      </c>
+      <c r="K26">
+        <v>215</v>
+      </c>
+      <c r="L26">
+        <v>1.2465120000000001</v>
+      </c>
+      <c r="M26">
+        <v>154</v>
+      </c>
+      <c r="N26" t="s">
+        <v>46</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>154</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>62</v>
+      </c>
+      <c r="R26">
+        <v>268</v>
+      </c>
+      <c r="S26">
+        <v>574.62686599999995</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>154</v>
+      </c>
+      <c r="W26">
+        <v>0.37313400000000002</v>
+      </c>
+      <c r="X26">
+        <v>2</v>
+      </c>
+      <c r="Y26">
+        <v>0.74626899999999996</v>
+      </c>
+      <c r="Z26">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>46</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>62</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>40</v>
+      </c>
+      <c r="K28">
+        <v>164</v>
+      </c>
+      <c r="L28">
+        <v>1.207317</v>
+      </c>
+      <c r="M28">
+        <v>121</v>
+      </c>
+      <c r="N28" t="s">
+        <v>46</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>121</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>62</v>
+      </c>
+      <c r="R28">
+        <v>198</v>
+      </c>
+      <c r="S28">
+        <v>611.11111100000005</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <v>121</v>
+      </c>
+      <c r="W28">
+        <v>0.50505100000000003</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>0.50505100000000003</v>
+      </c>
+      <c r="Z28">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29">
+        <v>27</v>
+      </c>
+      <c r="J29" t="s">
+        <v>40</v>
+      </c>
+      <c r="K29">
+        <v>1811</v>
+      </c>
+      <c r="L29">
+        <v>1.215903</v>
+      </c>
+      <c r="M29">
+        <v>85</v>
+      </c>
+      <c r="N29" t="s">
+        <v>46</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>2295</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>62</v>
+      </c>
+      <c r="R29">
+        <v>2202</v>
+      </c>
+      <c r="S29">
+        <v>1042.234332</v>
+      </c>
+      <c r="T29">
+        <v>27</v>
+      </c>
+      <c r="V29">
+        <v>85</v>
+      </c>
+      <c r="W29">
+        <v>1.2261580000000001</v>
+      </c>
+      <c r="X29">
+        <v>30</v>
+      </c>
+      <c r="Y29">
+        <v>1.362398</v>
+      </c>
+      <c r="Z29">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30">
+        <v>43</v>
+      </c>
+      <c r="J30" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30">
+        <v>695</v>
+      </c>
+      <c r="L30">
+        <v>1.3223020000000001</v>
+      </c>
+      <c r="M30">
+        <v>17.906976740000001</v>
+      </c>
+      <c r="N30" t="s">
+        <v>46</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>770</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>62</v>
+      </c>
+      <c r="R30">
+        <v>919</v>
+      </c>
+      <c r="S30">
+        <v>837.86724700000002</v>
+      </c>
+      <c r="T30">
+        <v>43</v>
+      </c>
+      <c r="V30">
+        <v>17.906977000000001</v>
+      </c>
+      <c r="W30">
+        <v>4.6789990000000001</v>
+      </c>
+      <c r="X30">
+        <v>53</v>
+      </c>
+      <c r="Y30">
+        <v>5.7671380000000001</v>
+      </c>
+      <c r="Z30">
+        <v>14.528302</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
+      <c r="J31" t="s">
+        <v>40</v>
+      </c>
+      <c r="K31">
+        <v>195</v>
+      </c>
+      <c r="L31">
+        <v>1.210256</v>
+      </c>
+      <c r="M31">
+        <v>47.333333330000002</v>
+      </c>
+      <c r="N31" t="s">
+        <v>46</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>142</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>62</v>
+      </c>
+      <c r="R31">
+        <v>236</v>
+      </c>
+      <c r="S31">
+        <v>601.69491500000004</v>
+      </c>
+      <c r="T31">
+        <v>3</v>
+      </c>
+      <c r="V31">
+        <v>47.333333000000003</v>
+      </c>
+      <c r="W31">
+        <v>1.2711859999999999</v>
+      </c>
+      <c r="X31">
+        <v>4</v>
+      </c>
+      <c r="Y31">
+        <v>1.6949149999999999</v>
+      </c>
+      <c r="Z31">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" t="s">
+        <v>54</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32">
+        <v>36</v>
+      </c>
+      <c r="L32">
+        <v>1.3055559999999999</v>
+      </c>
+      <c r="N32" t="s">
+        <v>46</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>9</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>62</v>
+      </c>
+      <c r="R32">
+        <v>47</v>
+      </c>
+      <c r="S32">
+        <v>191.489362</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>7</v>
+      </c>
+      <c r="J33" t="s">
+        <v>40</v>
+      </c>
+      <c r="K33">
+        <v>163</v>
+      </c>
+      <c r="L33">
+        <v>1.1901839999999999</v>
+      </c>
+      <c r="M33">
+        <v>22.14285714</v>
+      </c>
+      <c r="N33" t="s">
+        <v>46</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>155</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>62</v>
+      </c>
+      <c r="R33">
+        <v>194</v>
+      </c>
+      <c r="S33">
+        <v>798.96907199999998</v>
+      </c>
+      <c r="T33">
+        <v>7</v>
+      </c>
+      <c r="V33">
+        <v>22.142856999999999</v>
+      </c>
+      <c r="W33">
+        <v>3.608247</v>
+      </c>
+      <c r="X33">
+        <v>6</v>
+      </c>
+      <c r="Y33">
+        <v>3.092784</v>
+      </c>
+      <c r="Z33">
+        <v>25.833333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" t="s">
+        <v>54</v>
+      </c>
+      <c r="H34" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34">
+        <v>119</v>
+      </c>
+      <c r="J34" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34">
+        <v>1254</v>
+      </c>
+      <c r="L34">
+        <v>1.2551829999999999</v>
+      </c>
+      <c r="M34">
+        <v>15.008403360000001</v>
+      </c>
+      <c r="N34" t="s">
+        <v>46</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>1786</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>62</v>
+      </c>
+      <c r="R34">
+        <v>1574</v>
+      </c>
+      <c r="S34">
+        <v>1134.6886910000001</v>
+      </c>
+      <c r="T34">
+        <v>119</v>
+      </c>
+      <c r="V34">
+        <v>15.008402999999999</v>
+      </c>
+      <c r="W34">
+        <v>7.5603559999999996</v>
+      </c>
+      <c r="X34">
+        <v>130</v>
+      </c>
+      <c r="Y34">
+        <v>8.2592119999999998</v>
+      </c>
+      <c r="Z34">
+        <v>13.738462</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35">
+        <v>29</v>
+      </c>
+      <c r="J35" t="s">
+        <v>40</v>
+      </c>
+      <c r="K35">
+        <v>534</v>
+      </c>
+      <c r="L35">
+        <v>1.5262169999999999</v>
+      </c>
+      <c r="M35">
+        <v>41.137931029999997</v>
+      </c>
+      <c r="N35" t="s">
+        <v>46</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>1193</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>60</v>
+      </c>
+      <c r="R35">
+        <v>815</v>
+      </c>
+      <c r="S35">
+        <v>1463.8036810000001</v>
+      </c>
+      <c r="T35">
+        <v>29</v>
+      </c>
+      <c r="V35">
+        <v>41.137931000000002</v>
+      </c>
+      <c r="W35">
+        <v>3.5582820000000002</v>
+      </c>
+      <c r="X35">
+        <v>31</v>
+      </c>
+      <c r="Y35">
+        <v>3.8036810000000001</v>
+      </c>
+      <c r="Z35">
+        <v>38.483871000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
+        <v>35</v>
+      </c>
+      <c r="I36">
+        <v>8</v>
+      </c>
+      <c r="J36" t="s">
+        <v>40</v>
+      </c>
+      <c r="K36">
+        <v>334</v>
+      </c>
+      <c r="L36">
+        <v>1.464072</v>
+      </c>
+      <c r="M36">
+        <v>51.875</v>
+      </c>
+      <c r="N36" t="s">
+        <v>46</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>415</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>60</v>
+      </c>
+      <c r="R36">
+        <v>489</v>
+      </c>
+      <c r="S36">
+        <v>848.67075699999998</v>
+      </c>
+      <c r="T36">
+        <v>8</v>
+      </c>
+      <c r="V36">
+        <v>51.875</v>
+      </c>
+      <c r="W36">
+        <v>1.6359919999999999</v>
+      </c>
+      <c r="X36">
+        <v>8</v>
+      </c>
+      <c r="Y36">
+        <v>1.6359919999999999</v>
+      </c>
+      <c r="Z36">
+        <v>51.875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" t="s">
+        <v>40</v>
+      </c>
+      <c r="K37">
+        <v>64</v>
+      </c>
+      <c r="L37">
+        <v>1.34375</v>
+      </c>
+      <c r="M37">
+        <v>31</v>
+      </c>
+      <c r="N37" t="s">
+        <v>46</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>31</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>60</v>
+      </c>
+      <c r="R37">
+        <v>86</v>
+      </c>
+      <c r="S37">
+        <v>360.46511600000002</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+      <c r="V37">
+        <v>31</v>
+      </c>
+      <c r="W37">
+        <v>1.1627909999999999</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+      <c r="Y37">
+        <v>1.1627909999999999</v>
+      </c>
+      <c r="Z37">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38">
+        <v>7</v>
+      </c>
+      <c r="J38" t="s">
+        <v>40</v>
+      </c>
+      <c r="K38">
+        <v>473</v>
+      </c>
+      <c r="L38">
+        <v>1.2008460000000001</v>
+      </c>
+      <c r="M38">
+        <v>70.857142859999996</v>
+      </c>
+      <c r="N38" t="s">
+        <v>46</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>496</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>60</v>
+      </c>
+      <c r="R38">
+        <v>568</v>
+      </c>
+      <c r="S38">
+        <v>873.23943699999995</v>
+      </c>
+      <c r="T38">
+        <v>7</v>
+      </c>
+      <c r="V38">
+        <v>70.857142999999994</v>
+      </c>
+      <c r="W38">
+        <v>1.232394</v>
+      </c>
+      <c r="X38">
+        <v>8</v>
+      </c>
+      <c r="Y38">
+        <v>1.4084509999999999</v>
+      </c>
+      <c r="Z38">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39">
+        <v>741</v>
+      </c>
+      <c r="L39">
+        <v>1.17004</v>
+      </c>
+      <c r="M39">
+        <v>48.222222219999999</v>
+      </c>
+      <c r="N39" t="s">
+        <v>46</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>868</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>60</v>
+      </c>
+      <c r="R39">
+        <v>867</v>
+      </c>
+      <c r="S39">
+        <v>1001.153403</v>
+      </c>
+      <c r="T39">
+        <v>18</v>
+      </c>
+      <c r="V39">
+        <v>48.222222000000002</v>
+      </c>
+      <c r="W39">
+        <v>2.0761250000000002</v>
+      </c>
+      <c r="X39">
+        <v>19</v>
+      </c>
+      <c r="Y39">
+        <v>2.191465</v>
+      </c>
+      <c r="Z39">
+        <v>45.684210999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40">
+        <v>34</v>
+      </c>
+      <c r="J40" t="s">
+        <v>40</v>
+      </c>
+      <c r="K40">
+        <v>768</v>
+      </c>
+      <c r="L40">
+        <v>1.375</v>
+      </c>
+      <c r="M40">
+        <v>22.70588235</v>
+      </c>
+      <c r="N40" t="s">
+        <v>46</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>772</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>56</v>
+      </c>
+      <c r="R40">
+        <v>1056</v>
+      </c>
+      <c r="S40">
+        <v>731.06060600000001</v>
+      </c>
+      <c r="T40">
+        <v>34</v>
+      </c>
+      <c r="V40">
+        <v>22.705881999999999</v>
+      </c>
+      <c r="W40">
+        <v>3.219697</v>
+      </c>
+      <c r="X40">
+        <v>43</v>
+      </c>
+      <c r="Y40">
+        <v>4.0719700000000003</v>
+      </c>
+      <c r="Z40">
+        <v>17.953488</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>38</v>
+      </c>
+      <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41">
+        <v>98</v>
+      </c>
+      <c r="L41">
+        <v>1.2448980000000001</v>
+      </c>
+      <c r="N41" t="s">
+        <v>46</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>71</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>56</v>
+      </c>
+      <c r="R41">
+        <v>122</v>
+      </c>
+      <c r="S41">
+        <v>581.96721300000002</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>0.81967199999999996</v>
+      </c>
+      <c r="Z41">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42">
+        <v>10</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="N42" t="s">
+        <v>46</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>56</v>
+      </c>
+      <c r="R42">
+        <v>10</v>
+      </c>
+      <c r="S42">
+        <v>100</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>16</v>
+      </c>
+      <c r="J43" t="s">
+        <v>40</v>
+      </c>
+      <c r="K43">
+        <v>274</v>
+      </c>
+      <c r="L43">
+        <v>1.291971</v>
+      </c>
+      <c r="M43">
+        <v>17.8125</v>
+      </c>
+      <c r="N43" t="s">
+        <v>46</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>285</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>56</v>
+      </c>
+      <c r="R43">
+        <v>354</v>
+      </c>
+      <c r="S43">
+        <v>805.084746</v>
+      </c>
+      <c r="T43">
+        <v>16</v>
+      </c>
+      <c r="V43">
+        <v>17.8125</v>
+      </c>
+      <c r="W43">
+        <v>4.519774</v>
+      </c>
+      <c r="X43">
+        <v>18</v>
+      </c>
+      <c r="Y43">
+        <v>5.084746</v>
+      </c>
+      <c r="Z43">
+        <v>15.833333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" t="s">
+        <v>54</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>40</v>
+      </c>
+      <c r="K44">
+        <v>404</v>
+      </c>
+      <c r="L44">
+        <v>1.3391090000000001</v>
+      </c>
+      <c r="M44">
+        <v>27</v>
+      </c>
+      <c r="N44" t="s">
+        <v>46</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>567</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>56</v>
+      </c>
+      <c r="R44">
+        <v>541</v>
+      </c>
+      <c r="S44">
+        <v>1048.05915</v>
+      </c>
+      <c r="T44">
+        <v>21</v>
+      </c>
+      <c r="V44">
+        <v>27</v>
+      </c>
+      <c r="W44">
+        <v>3.8817010000000001</v>
+      </c>
+      <c r="X44">
+        <v>30</v>
+      </c>
+      <c r="Y44">
+        <v>5.5452870000000001</v>
+      </c>
+      <c r="Z44">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s">
+        <v>40</v>
+      </c>
+      <c r="K45">
+        <v>476</v>
+      </c>
+      <c r="L45">
+        <v>1.321429</v>
+      </c>
+      <c r="M45">
+        <v>20</v>
+      </c>
+      <c r="N45" t="s">
+        <v>46</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>400</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>56</v>
+      </c>
+      <c r="R45">
+        <v>629</v>
+      </c>
+      <c r="S45">
+        <v>635.93004800000006</v>
+      </c>
+      <c r="T45">
+        <v>20</v>
+      </c>
+      <c r="V45">
+        <v>20</v>
+      </c>
+      <c r="W45">
+        <v>3.1796500000000001</v>
+      </c>
+      <c r="X45">
+        <v>19</v>
+      </c>
+      <c r="Y45">
+        <v>3.0206680000000001</v>
+      </c>
+      <c r="Z45">
+        <v>21.052631999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" t="s">
+        <v>38</v>
+      </c>
+      <c r="F46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" t="s">
+        <v>54</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46" t="s">
+        <v>40</v>
+      </c>
+      <c r="K46">
+        <v>105</v>
+      </c>
+      <c r="L46">
+        <v>1.2285710000000001</v>
+      </c>
+      <c r="M46">
+        <v>47</v>
+      </c>
+      <c r="N46" t="s">
+        <v>46</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>47</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>56</v>
+      </c>
+      <c r="R46">
+        <v>129</v>
+      </c>
+      <c r="S46">
+        <v>364.34108500000002</v>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="V46">
+        <v>47</v>
+      </c>
+      <c r="W46">
+        <v>0.77519400000000005</v>
+      </c>
+      <c r="X46">
+        <v>2</v>
+      </c>
+      <c r="Y46">
+        <v>1.5503880000000001</v>
+      </c>
+      <c r="Z46">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F47" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47">
+        <v>17</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="N47" t="s">
+        <v>46</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>56</v>
+      </c>
+      <c r="R47">
+        <v>17</v>
+      </c>
+      <c r="S47">
+        <v>176.47058799999999</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" t="s">
+        <v>58</v>
+      </c>
+      <c r="D48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F48" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48">
+        <v>18</v>
+      </c>
+      <c r="J48" t="s">
+        <v>40</v>
+      </c>
+      <c r="K48">
+        <v>356</v>
+      </c>
+      <c r="L48">
+        <v>1.2359549999999999</v>
+      </c>
+      <c r="M48">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>46</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>306</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>56</v>
+      </c>
+      <c r="R48">
+        <v>440</v>
+      </c>
+      <c r="S48">
+        <v>695.45454500000005</v>
+      </c>
+      <c r="T48">
+        <v>18</v>
+      </c>
+      <c r="V48">
+        <v>17</v>
+      </c>
+      <c r="W48">
+        <v>4.0909089999999999</v>
+      </c>
+      <c r="X48">
         <v>26</v>
       </c>
-      <c r="N13" t="s">
-        <v>47</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>26</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>48</v>
-      </c>
-      <c r="R13">
-        <v>29</v>
-      </c>
-      <c r="S13">
-        <v>896.551724</v>
-      </c>
-      <c r="T13">
-        <v>1</v>
-      </c>
-      <c r="V13">
-        <v>26</v>
-      </c>
-      <c r="W13">
-        <v>3.448276</v>
-      </c>
-      <c r="X13">
-        <v>1</v>
-      </c>
-      <c r="Y13">
-        <v>3.448276</v>
-      </c>
-      <c r="Z13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="Y48">
+        <v>5.9090910000000001</v>
+      </c>
+      <c r="Z48">
+        <v>11.769231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" t="s">
+        <v>54</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>62</v>
+      </c>
+      <c r="J49" t="s">
+        <v>40</v>
+      </c>
+      <c r="K49">
+        <v>725</v>
+      </c>
+      <c r="L49">
+        <v>1.4013789999999999</v>
+      </c>
+      <c r="M49">
+        <v>15</v>
+      </c>
+      <c r="N49" t="s">
+        <v>46</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>930</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>56</v>
+      </c>
+      <c r="R49">
+        <v>1016</v>
+      </c>
+      <c r="S49">
+        <v>915.354331</v>
+      </c>
+      <c r="T49">
+        <v>62</v>
+      </c>
+      <c r="V49">
+        <v>15</v>
+      </c>
+      <c r="W49">
+        <v>6.1023620000000003</v>
+      </c>
+      <c r="X49">
+        <v>82</v>
+      </c>
+      <c r="Y49">
+        <v>8.0708660000000005</v>
+      </c>
+      <c r="Z49">
+        <v>11.341462999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>54</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50">
+        <v>231</v>
+      </c>
+      <c r="L50">
+        <v>1.2380949999999999</v>
+      </c>
+      <c r="M50">
+        <v>270</v>
+      </c>
+      <c r="N50" t="s">
+        <v>46</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>270</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>56</v>
+      </c>
+      <c r="R50">
+        <v>286</v>
+      </c>
+      <c r="S50">
+        <v>944.05594399999995</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="V50">
+        <v>270</v>
+      </c>
+      <c r="W50">
+        <v>0.34965000000000002</v>
+      </c>
+      <c r="X50">
+        <v>2</v>
+      </c>
+      <c r="Y50">
+        <v>0.69930099999999995</v>
+      </c>
+      <c r="Z50">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51" t="s">
+        <v>40</v>
+      </c>
+      <c r="K51">
+        <v>104</v>
+      </c>
+      <c r="L51">
+        <v>1.1923079999999999</v>
+      </c>
+      <c r="M51">
+        <v>59</v>
+      </c>
+      <c r="N51" t="s">
+        <v>46</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>59</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>56</v>
+      </c>
+      <c r="R51">
+        <v>124</v>
+      </c>
+      <c r="S51">
+        <v>475.80645199999998</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="V51">
+        <v>59</v>
+      </c>
+      <c r="W51">
+        <v>0.80645199999999995</v>
+      </c>
+      <c r="X51">
+        <v>2</v>
+      </c>
+      <c r="Y51">
+        <v>1.612903</v>
+      </c>
+      <c r="Z51">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" t="s">
+        <v>51</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" t="s">
+        <v>54</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="K52">
+        <v>9</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="N52" t="s">
+        <v>46</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>56</v>
+      </c>
+      <c r="R52">
+        <v>9</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="s">
+        <v>39</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53" t="s">
+        <v>40</v>
+      </c>
+      <c r="K53">
+        <v>147</v>
+      </c>
+      <c r="L53">
+        <v>1.306122</v>
+      </c>
+      <c r="M53">
+        <v>29.8</v>
+      </c>
+      <c r="N53" t="s">
+        <v>46</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>149</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>56</v>
+      </c>
+      <c r="R53">
+        <v>192</v>
+      </c>
+      <c r="S53">
+        <v>776.04166699999996</v>
+      </c>
+      <c r="T53">
+        <v>5</v>
+      </c>
+      <c r="V53">
+        <v>29.8</v>
+      </c>
+      <c r="W53">
+        <v>2.6041669999999999</v>
+      </c>
+      <c r="X53">
+        <v>7</v>
+      </c>
+      <c r="Y53">
+        <v>3.6458330000000001</v>
+      </c>
+      <c r="Z53">
+        <v>21.285713999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>54</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>55</v>
+      </c>
+      <c r="J54" t="s">
+        <v>40</v>
+      </c>
+      <c r="K54">
+        <v>786</v>
+      </c>
+      <c r="L54">
+        <v>1.2391859999999999</v>
+      </c>
+      <c r="M54">
+        <v>24.454545450000001</v>
+      </c>
+      <c r="N54" t="s">
+        <v>46</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>1345</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>56</v>
+      </c>
+      <c r="R54">
+        <v>974</v>
+      </c>
+      <c r="S54">
+        <v>1380.903491</v>
+      </c>
+      <c r="T54">
+        <v>55</v>
+      </c>
+      <c r="V54">
+        <v>24.454545</v>
+      </c>
+      <c r="W54">
+        <v>5.6468170000000004</v>
+      </c>
+      <c r="X54">
+        <v>57</v>
+      </c>
+      <c r="Y54">
+        <v>5.8521559999999999</v>
+      </c>
+      <c r="Z54">
+        <v>23.596491</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55" t="s">
+        <v>40</v>
+      </c>
+      <c r="K55">
+        <v>141</v>
+      </c>
+      <c r="L55">
+        <v>1.0709219999999999</v>
+      </c>
+      <c r="M55">
+        <v>86</v>
+      </c>
+      <c r="N55" t="s">
+        <v>46</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>172</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>53</v>
+      </c>
+      <c r="R55">
+        <v>151</v>
+      </c>
+      <c r="S55">
+        <v>1139.072848</v>
+      </c>
+      <c r="T55">
+        <v>2</v>
+      </c>
+      <c r="V55">
+        <v>86</v>
+      </c>
+      <c r="W55">
+        <v>1.324503</v>
+      </c>
+      <c r="X55">
+        <v>2</v>
+      </c>
+      <c r="Y55">
+        <v>1.324503</v>
+      </c>
+      <c r="Z55">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" t="s">
+        <v>54</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="K56">
+        <v>30</v>
+      </c>
+      <c r="L56">
+        <v>1.066667</v>
+      </c>
+      <c r="N56" t="s">
+        <v>46</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>18</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>53</v>
+      </c>
+      <c r="R56">
+        <v>32</v>
+      </c>
+      <c r="S56">
+        <v>562.5</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" t="s">
+        <v>51</v>
+      </c>
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" t="s">
+        <v>54</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="K57">
+        <v>8</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="N57" t="s">
+        <v>46</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>5</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>53</v>
+      </c>
+      <c r="R57">
+        <v>8</v>
+      </c>
+      <c r="S57">
+        <v>625</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" t="s">
+        <v>54</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58">
+        <v>5</v>
+      </c>
+      <c r="J58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K58">
+        <v>116</v>
+      </c>
+      <c r="L58">
+        <v>1.12069</v>
+      </c>
+      <c r="M58">
+        <v>30.6</v>
+      </c>
+      <c r="N58" t="s">
+        <v>46</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>153</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>53</v>
+      </c>
+      <c r="R58">
+        <v>130</v>
+      </c>
+      <c r="S58">
+        <v>1176.9230769999999</v>
+      </c>
+      <c r="T58">
+        <v>5</v>
+      </c>
+      <c r="V58">
+        <v>30.6</v>
+      </c>
+      <c r="W58">
+        <v>3.8461539999999999</v>
+      </c>
+      <c r="X58">
+        <v>7</v>
+      </c>
+      <c r="Y58">
+        <v>5.3846150000000002</v>
+      </c>
+      <c r="Z58">
+        <v>21.857143000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>28</v>
+      </c>
+      <c r="B59" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="s">
+        <v>41</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>10</v>
+      </c>
+      <c r="J59" t="s">
+        <v>40</v>
+      </c>
+      <c r="K59">
+        <v>157</v>
+      </c>
+      <c r="L59">
+        <v>1.0636939999999999</v>
+      </c>
+      <c r="M59">
+        <v>24.2</v>
+      </c>
+      <c r="N59" t="s">
+        <v>46</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>242</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>53</v>
+      </c>
+      <c r="R59">
+        <v>167</v>
+      </c>
+      <c r="S59">
+        <v>1449.1017959999999</v>
+      </c>
+      <c r="T59">
+        <v>10</v>
+      </c>
+      <c r="V59">
+        <v>24.2</v>
+      </c>
+      <c r="W59">
+        <v>5.9880240000000002</v>
+      </c>
+      <c r="X59">
+        <v>12</v>
+      </c>
+      <c r="Y59">
+        <v>7.1856289999999996</v>
+      </c>
+      <c r="Z59">
+        <v>20.166667</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="K60">
+        <v>3</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="N60" t="s">
+        <v>46</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>5</v>
+      </c>
+      <c r="Q60" t="s">
         <v>49</v>
       </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="R60">
+        <v>3</v>
+      </c>
+      <c r="S60">
+        <v>1666.666667</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>28</v>
+      </c>
+      <c r="B61" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" t="s">
+        <v>38</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="K61">
+        <v>2</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="N61" t="s">
+        <v>46</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>3</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>49</v>
+      </c>
+      <c r="R61">
+        <v>2</v>
+      </c>
+      <c r="S61">
+        <v>1500</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" t="s">
+        <v>39</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="K62">
+        <v>5</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="N62" t="s">
+        <v>46</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>3</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>49</v>
+      </c>
+      <c r="R62">
+        <v>5</v>
+      </c>
+      <c r="S62">
+        <v>600</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>40</v>
+      </c>
+      <c r="K63">
+        <v>45</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>79</v>
+      </c>
+      <c r="N63" t="s">
+        <v>46</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>79</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>49</v>
+      </c>
+      <c r="R63">
+        <v>45</v>
+      </c>
+      <c r="S63">
+        <v>1755.555556</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="V63">
+        <v>79</v>
+      </c>
+      <c r="W63">
+        <v>2.2222219999999999</v>
+      </c>
+      <c r="X63">
+        <v>1</v>
+      </c>
+      <c r="Y63">
+        <v>2.2222219999999999</v>
+      </c>
+      <c r="Z63">
+        <v>79</v>
+      </c>
+      <c r="AA63">
+        <v>1</v>
+      </c>
+      <c r="AB63">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" t="s">
         <v>32</v>
       </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14">
-        <v>6</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="N14" t="s">
-        <v>47</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>6</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>48</v>
-      </c>
-      <c r="R14">
-        <v>6</v>
-      </c>
-      <c r="S14">
+      <c r="F64" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" t="s">
+        <v>34</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="K64">
+        <v>21</v>
+      </c>
+      <c r="L64">
+        <v>1.0476190000000001</v>
+      </c>
+      <c r="N64" t="s">
+        <v>46</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>20</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>49</v>
+      </c>
+      <c r="R64">
+        <v>22</v>
+      </c>
+      <c r="S64">
+        <v>909.09090900000001</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>50</v>
+      </c>
+      <c r="D65" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" t="s">
+        <v>38</v>
+      </c>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="N65" t="s">
+        <v>46</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>49</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
         <v>1000</v>
       </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" t="s">
+        <v>51</v>
+      </c>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="N66" t="s">
+        <v>46</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="s">
         <v>49</v>
       </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15">
-        <v>4</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="N15" t="s">
-        <v>47</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>3</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>48</v>
-      </c>
-      <c r="R15">
-        <v>4</v>
-      </c>
-      <c r="S15">
-        <v>750</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" t="s">
+        <v>39</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="K67">
+        <v>8</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="N67" t="s">
+        <v>46</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>2</v>
+      </c>
+      <c r="Q67" t="s">
         <v>49</v>
       </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16">
-        <v>2</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="N16" t="s">
-        <v>47</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>48</v>
-      </c>
-      <c r="R16">
-        <v>2</v>
-      </c>
-      <c r="S16">
-        <v>1500</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="R67">
+        <v>8</v>
+      </c>
+      <c r="S67">
+        <v>250</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>28</v>
+      </c>
+      <c r="B68" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" t="s">
+        <v>50</v>
+      </c>
+      <c r="D68" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="s">
+        <v>34</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68" t="s">
+        <v>40</v>
+      </c>
+      <c r="K68">
+        <v>42</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>40</v>
+      </c>
+      <c r="N68" t="s">
+        <v>46</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>40</v>
+      </c>
+      <c r="Q68" t="s">
         <v>49</v>
       </c>
-      <c r="D17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17">
-        <v>27</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="N17" t="s">
-        <v>47</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>41</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>48</v>
-      </c>
-      <c r="R17">
-        <v>27</v>
-      </c>
-      <c r="S17">
-        <v>1518.518519</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
+      <c r="R68">
+        <v>42</v>
+      </c>
+      <c r="S68">
+        <v>952.38095199999998</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="V68">
+        <v>40</v>
+      </c>
+      <c r="W68">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="X68">
+        <v>1</v>
+      </c>
+      <c r="Y68">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="Z68">
+        <v>40</v>
+      </c>
+      <c r="AA68">
+        <v>1</v>
+      </c>
+      <c r="AB68">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>